--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487563_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487563_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>16.27</v>
+        <v>16.0445</v>
       </c>
       <c r="E2" t="n">
-        <v>12.803</v>
+        <v>12.6577</v>
       </c>
       <c r="F2" t="n">
-        <v>3.467</v>
+        <v>3.3868</v>
       </c>
       <c r="G2" t="n">
         <v>11.8232</v>
@@ -610,13 +610,13 @@
         <v>4.7004</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1922</v>
+        <v>0.9667</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7399</v>
+        <v>0.5946</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4523</v>
+        <v>0.3721</v>
       </c>
       <c r="V2" t="n">
         <v>1.492</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.067</v>
+        <v>5.5298</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6168</v>
+        <v>6.0262</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.4964</v>
       </c>
       <c r="G3" t="n">
         <v>3.6892</v>
@@ -688,13 +688,13 @@
         <v>2.9377</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2074</v>
+        <v>0.6702</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1059</v>
+        <v>0.5152</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1015</v>
+        <v>0.155</v>
       </c>
       <c r="V3" t="n">
         <v>-1.7673</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GRANDA</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.916</v>
+        <v>4.6563</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0372</v>
+        <v>4.1225</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1212</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4292</v>
+        <v>3.0051</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6267</v>
+        <v>0.1612</v>
       </c>
       <c r="I4" t="n">
-        <v>2.056</v>
+        <v>2.8439</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5083</v>
+        <v>3.0572</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0033</v>
+        <v>0.4966</v>
       </c>
       <c r="L4" t="n">
-        <v>1.505</v>
+        <v>2.5606</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0791</v>
+        <v>-0.0521</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6301</v>
+        <v>-0.3354</v>
       </c>
       <c r="O4" t="n">
-        <v>0.551</v>
+        <v>0.2833</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3502</v>
+        <v>2.546</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3502</v>
+        <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>0.587</v>
+        <v>-0.2866</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4286</v>
+        <v>0.457</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8416</v>
+        <v>-0.7435</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5495</v>
+        <v>-0.6083</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1003</v>
+        <v>0.6083</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5507</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>S. MARTINEZ GRANDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0585</v>
+        <v>4.0171</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5514</v>
+        <v>4.2185</v>
       </c>
       <c r="F5" t="n">
-        <v>0.507</v>
+        <v>-0.2014</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0051</v>
+        <v>0.4292</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1612</v>
+        <v>-1.6267</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8439</v>
+        <v>2.056</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0572</v>
+        <v>1.5083</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4966</v>
+        <v>0.0033</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5606</v>
+        <v>1.505</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0521</v>
+        <v>-1.0791</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3354</v>
+        <v>-1.6301</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2833</v>
+        <v>0.551</v>
       </c>
       <c r="P5" t="n">
-        <v>2.546</v>
+        <v>2.3502</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.546</v>
+        <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8844</v>
+        <v>-0.3119</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1141</v>
+        <v>0.6099</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7703</v>
+        <v>-0.9218</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6083</v>
+        <v>1.5495</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6083</v>
+        <v>2.1003</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2166</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>M. GARCIA FRAGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1909</v>
+        <v>1.4786</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3389</v>
+        <v>-0.9591</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.148</v>
+        <v>2.4377</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1708</v>
+        <v>0.4962</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0185</v>
+        <v>-1.4441</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1524</v>
+        <v>1.9403</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8199</v>
+        <v>0.3453</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0664</v>
+        <v>-1.3118</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7534</v>
+        <v>1.657</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.351</v>
+        <v>0.151</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.952</v>
+        <v>-0.1323</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.399</v>
+        <v>0.2833</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1543</v>
+        <v>0.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1543</v>
+        <v>2.3502</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4827</v>
+        <v>-0.0176</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3339</v>
+        <v>0.3788</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1489</v>
+        <v>-0.3964</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8249</v>
+        <v>0.2754</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1003</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8522</v>
+        <v>0.4537</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1388</v>
+        <v>1.682</v>
       </c>
       <c r="F7" t="n">
-        <v>1.991</v>
+        <v>-1.2282</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4598</v>
+        <v>-2.1708</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.5002</v>
+        <v>-1.0185</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0404</v>
+        <v>-1.1524</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0432</v>
+        <v>-0.8199</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2097</v>
+        <v>-0.0664</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1665</v>
+        <v>-0.7534</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4166</v>
+        <v>-1.351</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2905</v>
+        <v>-0.952</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1261</v>
+        <v>-0.399</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3709</v>
+        <v>2.1543</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.3294</v>
+        <v>2.1543</v>
       </c>
       <c r="S7" t="n">
-        <v>1.115</v>
+        <v>0.7456</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0369</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0781</v>
+        <v>0.0687</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8260999999999999</v>
+        <v>-0.2754</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8260999999999999</v>
+        <v>1.8249</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. GARCIA FRAGA</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7074</v>
+        <v>0.293</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8372</v>
+        <v>-1.591</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5446</v>
+        <v>1.884</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4962</v>
+        <v>-2.4598</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4441</v>
+        <v>-2.5002</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9403</v>
+        <v>0.0404</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3453</v>
+        <v>-1.0432</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3118</v>
+        <v>-1.2097</v>
       </c>
       <c r="L8" t="n">
-        <v>1.657</v>
+        <v>0.1665</v>
       </c>
       <c r="M8" t="n">
-        <v>0.151</v>
+        <v>-1.4166</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1323</v>
+        <v>-1.2905</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2833</v>
+        <v>-0.1261</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3502</v>
+        <v>3.3294</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7887999999999999</v>
+        <v>0.5558</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4993</v>
+        <v>0.5846</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2895</v>
+        <v>-0.0288</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6083</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2754</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06370000000000001</v>
+        <v>0.2096</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1925</v>
+        <v>-0.1331</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1288</v>
+        <v>0.3427</v>
       </c>
       <c r="G9" t="n">
         <v>1.9932</v>
@@ -1156,13 +1156,13 @@
         <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3679</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3258</v>
+        <v>0.3852</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6938</v>
+        <v>-0.4799</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1014</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0714</v>
+        <v>-1.0447</v>
       </c>
       <c r="E10" t="n">
         <v>-1.5427</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4713</v>
+        <v>0.498</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7728</v>
@@ -1234,13 +1234,13 @@
         <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1604</v>
+        <v>-0.1337</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V10" t="n">
         <v>0.6659</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4894</v>
+        <v>-1.1153</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8272</v>
+        <v>-1.8698</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3379</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7358</v>
+        <v>0.5901</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5238</v>
+        <v>-0.8489</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7879</v>
+        <v>1.439</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8087</v>
+        <v>0.5756</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.778</v>
+        <v>-0.5802</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0308</v>
+        <v>1.1557</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0145</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7458</v>
+        <v>-0.2687</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8187</v>
+        <v>0.2833</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1543</v>
+        <v>2.546</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0495</v>
+        <v>-0.3724</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1139</v>
+        <v>0.217</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0645</v>
+        <v>-0.5895</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9988</v>
+        <v>-0.9412</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.2754</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8249</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0247</v>
+        <v>-2.3134</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6455</v>
+        <v>-3.6479</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6209</v>
+        <v>1.3345</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5901</v>
+        <v>-3.2983</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8489</v>
+        <v>-2.0146</v>
       </c>
       <c r="I12" t="n">
-        <v>1.439</v>
+        <v>-1.2836</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5756</v>
+        <v>-1.6765</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5802</v>
+        <v>-0.5189</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1557</v>
+        <v>-1.1576</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0145</v>
+        <v>-1.6218</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2687</v>
+        <v>-1.4957</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2833</v>
+        <v>-0.1261</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R12" t="n">
-        <v>2.546</v>
+        <v>2.7419</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2818</v>
+        <v>0.2014</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5587</v>
+        <v>-0.0129</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7231</v>
+        <v>0.2144</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9412</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.245</v>
+        <v>-2.4474</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.526</v>
+        <v>-2.7318</v>
       </c>
       <c r="F13" t="n">
-        <v>1.281</v>
+        <v>0.2844</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.2983</v>
+        <v>-1.7358</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.0146</v>
+        <v>-2.5238</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2836</v>
+        <v>0.7879</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6765</v>
+        <v>-1.8087</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5189</v>
+        <v>-1.778</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1576</v>
+        <v>-0.0308</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6218</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4957</v>
+        <v>-0.7458</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1261</v>
+        <v>0.8187</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7419</v>
+        <v>2.1543</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7301</v>
+        <v>0.0915</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.891</v>
+        <v>0.2094</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1609</v>
+        <v>-0.1179</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.9988</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.1678</v>
+        <v>25.7618</v>
       </c>
       <c r="E14" t="n">
-        <v>15.6374</v>
+        <v>16.2315</v>
       </c>
       <c r="F14" t="n">
-        <v>9.530400000000002</v>
+        <v>9.5304</v>
       </c>
       <c r="G14" t="n">
         <v>10.5887</v>
@@ -1522,13 +1522,13 @@
         <v>18.9583</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3435</v>
+        <v>2.343499999999999</v>
       </c>
       <c r="L14" t="n">
         <v>16.6145</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.3696</v>
+        <v>-8.369599999999998</v>
       </c>
       <c r="N14" t="n">
         <v>-9.1555</v>
@@ -1546,13 +1546,13 @@
         <v>29.3771</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4204</v>
+        <v>2.0143</v>
       </c>
       <c r="T14" t="n">
-        <v>3.843599999999999</v>
+        <v>4.437499999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.4233</v>
+        <v>-2.423</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5505999999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>D. LASTRA GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2113</v>
+        <v>0.9101</v>
       </c>
       <c r="E15" t="n">
-        <v>2.835</v>
+        <v>1.0472</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6237</v>
+        <v>-0.1372</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.4645</v>
+        <v>0.5541</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.505</v>
+        <v>0.8166</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9596</v>
+        <v>-0.2625</v>
       </c>
       <c r="J15" t="n">
+        <v>1.0208</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.0208</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.4667</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.2042</v>
+      </c>
+      <c r="O15" t="n">
         <v>-0.2625</v>
       </c>
-      <c r="K15" t="n">
-        <v>-0.3029</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.0404</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-2.2021</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.2021</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-2</v>
-      </c>
       <c r="P15" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8132</v>
+        <v>0.1601</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2714</v>
+        <v>0.0265</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.1337</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3124</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. LASTRA GONZALEZ</t>
+          <t>D. REIRIZ MENDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6252</v>
+        <v>-0.0009</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8425</v>
+        <v>-0.6875</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2174</v>
+        <v>0.6866</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5541</v>
+        <v>0.4466</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8166</v>
+        <v>0.7091</v>
       </c>
       <c r="I16" t="n">
         <v>-0.2625</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0208</v>
+        <v>0.0935</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0208</v>
+        <v>0.7758</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.6822</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4667</v>
+        <v>0.3531</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2042</v>
+        <v>-0.0667</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2625</v>
+        <v>0.4197</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1247</v>
+        <v>0.6112</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1782</v>
+        <v>0.394</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0535</v>
+        <v>0.2172</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. REIRIZ MENDEZ</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.319</v>
+        <v>-0.0692</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0735</v>
+        <v>1.7093</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3925</v>
+        <v>-1.7785</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4466</v>
+        <v>-2.4645</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7091</v>
+        <v>-0.505</v>
       </c>
       <c r="I17" t="n">
+        <v>-1.9596</v>
+      </c>
+      <c r="J17" t="n">
         <v>-0.2625</v>
       </c>
-      <c r="J17" t="n">
-        <v>0.0935</v>
-      </c>
       <c r="K17" t="n">
-        <v>0.7758</v>
+        <v>-0.3029</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6822</v>
+        <v>0.0404</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3531</v>
+        <v>-2.2021</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0667</v>
+        <v>-0.2021</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4197</v>
+        <v>-2</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9312</v>
+        <v>1.5327</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0081</v>
+        <v>1.1457</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0769</v>
+        <v>0.387</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2754</v>
+        <v>-0.3124</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2754</v>
+        <v>-1.1385</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1078</v>
+        <v>-0.1343</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6633</v>
+        <v>4.0726</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.7711</v>
+        <v>-4.207</v>
       </c>
       <c r="G18" t="n">
         <v>1.4633</v>
@@ -1858,13 +1858,13 @@
         <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6204</v>
+        <v>-0.6469</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1317</v>
+        <v>0.2776</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.4887</v>
+        <v>-0.9245</v>
       </c>
       <c r="V18" t="n">
         <v>1.0078</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4125</v>
+        <v>-0.8547</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6886</v>
+        <v>0.8933</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1011</v>
+        <v>-1.748</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1978</v>
@@ -1936,13 +1936,13 @@
         <v>1.5668</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2516</v>
+        <v>-0.6939</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.517</v>
+        <v>-0.3123</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7346</v>
+        <v>-0.3815</v>
       </c>
       <c r="V19" t="n">
         <v>2.3871</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9858</v>
+        <v>-1.7381</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1427</v>
+        <v>-1.4375</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8431</v>
+        <v>-0.3006</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7111</v>
+        <v>-3.3123</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6148</v>
+        <v>-1.3828</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0964</v>
+        <v>-1.9295</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6128</v>
+        <v>-1.7821</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4168</v>
+        <v>-1.1807</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0297</v>
+        <v>-0.6014</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.324</v>
+        <v>-1.5302</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1979</v>
+        <v>-0.2021</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1261</v>
+        <v>-1.3281</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3917</v>
+        <v>1.7626</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>1.7626</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2364</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1235</v>
+        <v>0.3446</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3599</v>
+        <v>-0.2692</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3535</v>
+        <v>-0.2638</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0781</v>
+        <v>-0.2638</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.705</v>
+        <v>-2.0318</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8691</v>
+        <v>-1.245</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.836</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06320000000000001</v>
+        <v>-1.7111</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6587</v>
+        <v>-0.6148</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5955</v>
+        <v>-1.0964</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6528</v>
+        <v>0.6128</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9254</v>
+        <v>-0.4168</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7275</v>
+        <v>1.0297</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5896</v>
+        <v>-2.324</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2667</v>
+        <v>-0.1979</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3229</v>
+        <v>-2.1261</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1751</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1336</v>
+        <v>-2.1543</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9585</v>
+        <v>1.7626</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5647</v>
+        <v>-0.2824</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6693</v>
+        <v>0.0212</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1046</v>
+        <v>-0.3036</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1578</v>
+        <v>0.3535</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0576</v>
+        <v>0.2754</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1003</v>
+        <v>0.0781</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2261</v>
+        <v>-2.616</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3585</v>
+        <v>-1.5633</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8676</v>
+        <v>-1.0527</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3123</v>
+        <v>-0.97</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3828</v>
+        <v>0.2825</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9295</v>
+        <v>-1.2525</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7821</v>
+        <v>0.2237</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1807</v>
+        <v>0.1429</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6014</v>
+        <v>0.0808</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5302</v>
+        <v>-1.1938</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2021</v>
+        <v>0.1396</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3281</v>
+        <v>-1.3333</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7626</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4125</v>
+        <v>0.1754</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5764</v>
+        <v>-0.0659</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8361</v>
+        <v>0.2413</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2638</v>
+        <v>0.3329</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2638</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.242</v>
+        <v>-3.7689</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9726</v>
+        <v>-1.5854</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2694</v>
+        <v>-2.1835</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.97</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2825</v>
+        <v>0.6587</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2525</v>
+        <v>-0.5955</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2237</v>
+        <v>1.6528</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1429</v>
+        <v>0.9254</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0808</v>
+        <v>0.7275</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1938</v>
+        <v>-1.5896</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1396</v>
+        <v>-0.2667</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3333</v>
+        <v>-1.3229</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1543</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9377</v>
+        <v>-3.1336</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7834</v>
+        <v>1.9585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4506</v>
+        <v>-0.4992</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4752</v>
+        <v>-0.0471</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0246</v>
+        <v>-0.4521</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3329</v>
+        <v>-2.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2166</v>
+        <v>-0.0576</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8837</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2694</v>
+        <v>-4.5724</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7473</v>
+        <v>-2.1333</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.522</v>
+        <v>-2.439</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3815</v>
@@ -2326,13 +2326,13 @@
         <v>1.9585</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.299</v>
+        <v>-0.602</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4399</v>
+        <v>0.1741</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.859</v>
+        <v>-0.776</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4139</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.3749</v>
+        <v>-8.927099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.396100000000001</v>
+        <v>-8.6008</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0213</v>
+        <v>-0.3262</v>
       </c>
       <c r="G25" t="n">
         <v>-3.0787</v>
@@ -2404,13 +2404,13 @@
         <v>2.1543</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.1137</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6693</v>
+        <v>0.4646</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0035</v>
+        <v>-0.351</v>
       </c>
       <c r="V25" t="n">
         <v>0.8927</v>
@@ -2437,31 +2437,31 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-25.168</v>
+        <v>-23.8033</v>
       </c>
       <c r="E26" t="n">
         <v>-9.5304</v>
       </c>
       <c r="F26" t="n">
-        <v>-15.6376</v>
+        <v>-14.2729</v>
       </c>
       <c r="G26" t="n">
         <v>-10.5887</v>
       </c>
       <c r="H26" t="n">
-        <v>6.811900000000001</v>
+        <v>6.8119</v>
       </c>
       <c r="I26" t="n">
         <v>-17.4007</v>
       </c>
       <c r="J26" t="n">
-        <v>8.369400000000002</v>
+        <v>8.369400000000001</v>
       </c>
       <c r="K26" t="n">
         <v>9.155799999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.7858999999999999</v>
+        <v>-0.7858999999999998</v>
       </c>
       <c r="M26" t="n">
         <v>-18.9584</v>
@@ -2482,13 +2482,13 @@
         <v>15.6678</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.4203</v>
+        <v>-0.05590000000000009</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4232</v>
+        <v>2.423</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.8434</v>
+        <v>-2.4787</v>
       </c>
       <c r="V26" t="n">
         <v>0.5507000000000004</v>
